--- a/data/trans_orig/IP16A98-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A98-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6586</t>
+          <t>6618</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7327</t>
+          <t>7369</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11848</t>
+          <t>12284</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15995</t>
+          <t>15963</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21336</t>
+          <t>21314</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9476</t>
+          <t>9434</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14957</t>
+          <t>15252</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27536</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35416</t>
+          <t>35587</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>90,36%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7416</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17247</t>
+          <t>17439</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>9731</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21239</t>
+          <t>21509</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18580</t>
+          <t>19073</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34617</t>
+          <t>35422</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68993</t>
+          <t>68801</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78824</t>
+          <t>79223</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78560</t>
+          <t>78290</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90695</t>
+          <t>90068</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>151422</t>
+          <t>150617</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>167459</t>
+          <t>166966</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,75%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>746</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6471</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13780</t>
+          <t>13193</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29324</t>
+          <t>29328</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35089</t>
+          <t>35049</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28082</t>
+          <t>28703</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35530</t>
+          <t>35906</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59968</t>
+          <t>60555</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69552</t>
+          <t>69673</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,47%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11723</t>
+          <t>11808</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24369</t>
+          <t>24872</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16546</t>
+          <t>16488</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31573</t>
+          <t>31501</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32332</t>
+          <t>31577</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51727</t>
+          <t>51700</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>119744</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>132893</t>
+          <t>132808</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>122982</t>
+          <t>123054</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>138009</t>
+          <t>138067</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>247444</t>
+          <t>247471</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>266839</t>
+          <t>267594</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,45%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>7031</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2447</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9247</t>
+          <t>8474</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>34,62%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8776</t>
+          <t>8660</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14454</t>
+          <t>14463</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15230</t>
+          <t>16003</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22030</t>
+          <t>22456</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>91,74%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8933</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20224</t>
+          <t>20644</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12878</t>
+          <t>13449</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25392</t>
+          <t>26362</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24584</t>
+          <t>25114</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41046</t>
+          <t>41909</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,86%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62755</t>
+          <t>62335</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74046</t>
+          <t>74150</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60228</t>
+          <t>59258</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72742</t>
+          <t>72171</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>127553</t>
+          <t>126690</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>144015</t>
+          <t>143485</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,1%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1419</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7284</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2587</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9671</t>
+          <t>9764</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5279</t>
+          <t>5626</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14773</t>
+          <t>14746</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,57%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21475</t>
+          <t>21508</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27373</t>
+          <t>27524</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19199</t>
+          <t>19106</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26283</t>
+          <t>26671</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42888</t>
+          <t>42915</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52382</t>
+          <t>52035</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,24%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15703</t>
+          <t>15240</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29345</t>
+          <t>29441</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18317</t>
+          <t>19022</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33834</t>
+          <t>33523</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37240</t>
+          <t>37927</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56783</t>
+          <t>58056</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98116</t>
+          <t>98020</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111758</t>
+          <t>112221</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>89442</t>
+          <t>89753</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>104959</t>
+          <t>104254</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>193954</t>
+          <t>192681</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>213497</t>
+          <t>212810</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13571</t>
+          <t>13278</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20370</t>
+          <t>20110</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,09%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13348</t>
+          <t>13285</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9635</t>
+          <t>9325</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15026</t>
+          <t>14999</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10527</t>
+          <t>10787</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26743</t>
+          <t>26711</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,45%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7569</t>
+          <t>8156</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26284</t>
+          <t>26950</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17059</t>
+          <t>17229</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37042</t>
+          <t>37560</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29160</t>
+          <t>28196</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56854</t>
+          <t>56350</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94559</t>
+          <t>93893</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>113274</t>
+          <t>112687</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82982</t>
+          <t>82464</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>102965</t>
+          <t>102795</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>184013</t>
+          <t>184517</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>211707</t>
+          <t>212671</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,29%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>4388</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12255</t>
+          <t>12471</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12964</t>
+          <t>13528</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8948</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21275</t>
+          <t>21341</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,21%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29387</t>
+          <t>29171</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37310</t>
+          <t>37254</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33547</t>
+          <t>32983</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43522</t>
+          <t>43781</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66878</t>
+          <t>66812</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>79205</t>
+          <t>79625</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,33%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19656</t>
+          <t>19615</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>49092</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24660</t>
+          <t>23963</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45555</t>
+          <t>46435</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46865</t>
+          <t>49549</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85107</t>
+          <t>86352</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>127797</t>
+          <t>128623</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158059</t>
+          <t>158100</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>136646</t>
+          <t>135766</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>157541</t>
+          <t>158238</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>274809</t>
+          <t>273564</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>313051</t>
+          <t>310367</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,23%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A98-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A98-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4130</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1668</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7799</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>24,58%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9,93%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>46,41%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3235</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1267</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6618</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1268</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7184</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>14,33%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,61%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>29,31%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4130</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1551</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7369</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>24,58%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>12525</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12673</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9004</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>15135</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>75,42%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>53,59%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>90,07%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>19346</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15963</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>21314</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15397</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>21313</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>85,67%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>70,69%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12673</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9434</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>15252</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>75,42%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27100</t>
+          <t>26859</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35587</t>
+          <t>35243</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>89,49%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16803</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16803</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16803</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>22581</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>22581</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>22581</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>16803</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>16803</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>16803</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14259</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8806</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>20884</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14,29%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8,82%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20,93%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>11451</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7017</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17439</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7307</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>17174</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>13,28%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,14%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20,22%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>14259</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>9731</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>21509</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>14,29%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19073</t>
+          <t>18405</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35422</t>
+          <t>34023</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>85540</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>78915</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>90993</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>85,71%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>79,07%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>91,18%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>74789</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>68801</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>79223</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>69066</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>78933</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>86,72%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>79,78%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,86%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>85540</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>78290</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>90068</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>85,71%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>150617</t>
+          <t>152016</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>166966</t>
+          <t>167634</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>90,11%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>99799</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>99799</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>99799</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>86240</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>86240</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>86240</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>99799</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>99799</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>99799</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5086</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2452</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9596</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,4%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,46%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>25,28%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2788</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>746</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6467</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6344</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>7,79%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,07%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5086</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9251</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>13,4%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13193</t>
+          <t>13716</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>32868</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>28358</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>35502</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>86,6%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>74,72%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,54%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>33007</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>29328</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>35049</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>29451</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>35070</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>92,21%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>81,93%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,92%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>32868</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>28703</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>35906</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>86,6%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60555</t>
+          <t>60032</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69673</t>
+          <t>69421</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,13%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>37954</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>37954</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>37954</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>35795</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>35795</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>35795</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>37954</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>37954</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>37954</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23475</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>16896</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>31398</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15,19%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,93%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20,32%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>17473</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>11808</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>24872</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>11807</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>24464</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>12,08%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>8,16%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>17,2%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>23475</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>16488</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>31501</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>15,19%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31577</t>
+          <t>31850</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51700</t>
+          <t>51779</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>131080</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>123157</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>137659</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>84,81%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>79,68%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,07%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>127143</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>119744</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>132808</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>120152</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>132809</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>87,92%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>82,8%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>83,08%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>91,84%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>131080</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>123054</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>138067</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>84,81%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>79,62%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>89,33%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>366</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>247471</t>
+          <t>247392</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>267594</t>
+          <t>267321</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,35%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>154555</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>154555</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>154555</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>144616</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>144616</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>144616</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>154555</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>154555</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>154555</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2325,72 +2325,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4314</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>15,95%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>49,11%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3503</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1228</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7031</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7048</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>22,32%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>44,81%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1401</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4383</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>15,95%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8474</t>
+          <t>8883</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>36,29%</t>
         </is>
       </c>
     </row>
@@ -2438,72 +2438,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7385</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4472</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>84,05%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>50,89%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>12188</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8660</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14463</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8643</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>14370</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>77,68%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>55,19%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>92,17%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>7385</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>4403</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>84,05%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16003</t>
+          <t>15594</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22456</t>
+          <t>22347</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,3%</t>
         </is>
       </c>
     </row>
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>15691</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>15691</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>15691</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2668,72 +2668,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18422</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12867</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24714</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>21,52%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>15,03%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>28,87%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>14309</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8829</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>20644</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>20590</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>17,24%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10,64%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,88%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>18422</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>13449</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>26362</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>21,52%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25114</t>
+          <t>24788</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41909</t>
+          <t>42082</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -2781,72 +2781,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>67198</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>60906</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>72753</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>78,48%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>71,13%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>84,97%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>68670</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>62335</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>74150</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>62389</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>73774</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>82,76%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>89,36%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>67198</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>59258</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>72171</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>78,48%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>126690</t>
+          <t>126517</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>143485</t>
+          <t>143811</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,3%</t>
         </is>
       </c>
     </row>
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>82979</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>82979</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>82979</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3011,72 +3011,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5221</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2507</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9474</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>18,08%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,68%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>32,82%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3855</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1268</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7284</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1365</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7563</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>13,39%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>25,3%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5221</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2199</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9764</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>18,08%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14746</t>
+          <t>14116</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -3124,72 +3124,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>23649</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>19396</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>26363</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>81,92%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>67,18%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,32%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>24937</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>21508</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>27524</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>21229</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>27427</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>86,61%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>74,7%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,6%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>23649</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>19106</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>26671</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>81,92%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42915</t>
+          <t>43545</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52035</t>
+          <t>52494</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>91,04%</t>
         </is>
       </c>
     </row>
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>28792</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>28792</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>28792</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3354,72 +3354,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18186</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33081</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>20,32%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,75%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>26,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>21668</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15240</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>29441</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>14773</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>29092</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>17,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11,96%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>23,1%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>25045</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>19022</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>33523</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>20,32%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37927</t>
+          <t>37429</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58056</t>
+          <t>57146</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -3467,72 +3467,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>98231</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>90195</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>105090</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>79,68%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>73,17%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,25%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>105793</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>98020</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>112221</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>98369</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>112688</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>83,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>76,9%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>88,04%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>98231</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>89753</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>104254</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>79,68%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>192681</t>
+          <t>193591</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>212810</t>
+          <t>213308</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>85,07%</t>
         </is>
       </c>
     </row>
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>127461</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3933,32 +3933,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7699</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>857</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13278</t>
+          <t>6126</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3968,32 +3968,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>2422</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>809</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4003,32 +4003,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10399</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20110</t>
+          <t>8975</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>37,87%</t>
         </is>
       </c>
     </row>
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11385</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7794</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13063</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>81,79%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>55,99%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>93,84%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7531</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13285</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>49,45%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>12,82%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>87,23%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12966</t>
+          <t>7359</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9325</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14999</t>
+          <t>8972</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4116,32 +4116,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>20498</t>
+          <t>18744</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10787</t>
+          <t>14726</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26711</t>
+          <t>21565</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>90,99%</t>
         </is>
       </c>
     </row>
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4229,17 +4229,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4271,72 +4271,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21483</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>14803</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>34418</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>19,91%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13,72%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>31,89%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>17398</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8156</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>26950</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>14,4%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,75%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>22,3%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24426</t>
+          <t>17558</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17229</t>
+          <t>12065</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37560</t>
+          <t>24311</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>41823</t>
+          <t>39041</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28196</t>
+          <t>29838</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56350</t>
+          <t>52456</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -4384,72 +4384,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>86429</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>73494</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>93109</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>80,09%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>68,11%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>86,28%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>103445</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>93893</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>112687</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>85,6%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>77,7%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,25%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>95598</t>
+          <t>75126</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82464</t>
+          <t>68373</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>102795</t>
+          <t>80619</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4459,32 +4459,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>199044</t>
+          <t>161555</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>184517</t>
+          <t>148140</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>212671</t>
+          <t>170758</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>85,13%</t>
         </is>
       </c>
     </row>
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4614,72 +4614,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6275</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2513</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12279</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>14,55%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>28,48%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7646</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4388</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12471</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>18,36%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>29,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>7832</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13528</t>
+          <t>12765</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4689,32 +4689,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14036</t>
+          <t>14107</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>8855</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21341</t>
+          <t>21210</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -4727,72 +4727,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>36844</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>30840</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>40606</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>85,45%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>71,52%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,17%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>33996</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>29171</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>37254</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>81,64%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>70,05%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>89,46%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40121</t>
+          <t>32695</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32983</t>
+          <t>27762</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43781</t>
+          <t>36242</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4802,32 +4802,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>74117</t>
+          <t>69540</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66812</t>
+          <t>62437</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>79625</t>
+          <t>74792</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>89,41%</t>
         </is>
       </c>
     </row>
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4915,17 +4915,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4957,72 +4957,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>30293</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>21832</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>42758</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18,36%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>13,24%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>25,92%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>32743</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>19615</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>49092</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>18,42%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11,04%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>27,62%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33516</t>
+          <t>27812</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23963</t>
+          <t>20372</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46435</t>
+          <t>35456</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5032,32 +5032,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>66259</t>
+          <t>58105</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49549</t>
+          <t>46288</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86352</t>
+          <t>71920</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -5070,72 +5070,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>134659</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>122194</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>143120</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>81,64%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>74,08%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>86,76%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>144972</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>128623</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>158100</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>81,58%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>72,38%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>88,96%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>148685</t>
+          <t>115180</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>135766</t>
+          <t>107536</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>158238</t>
+          <t>122620</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5145,32 +5145,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>293657</t>
+          <t>249839</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>273564</t>
+          <t>236024</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>310367</t>
+          <t>261656</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>84,97%</t>
         </is>
       </c>
     </row>
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5258,17 +5258,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
